--- a/artfynd/A 18629-2024 artfynd.xlsx
+++ b/artfynd/A 18629-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980703</v>
+        <v>117980657</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>79561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593374</v>
+        <v>593361</v>
       </c>
       <c r="R3" t="n">
-        <v>6982518</v>
+        <v>6982517</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980657</v>
+        <v>117980703</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>97753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593361</v>
+        <v>593374</v>
       </c>
       <c r="R4" t="n">
-        <v>6982517</v>
+        <v>6982518</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>

--- a/artfynd/A 18629-2024 artfynd.xlsx
+++ b/artfynd/A 18629-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980611</v>
+        <v>117980691</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593353</v>
+        <v>593266</v>
       </c>
       <c r="R2" t="n">
-        <v>6982492</v>
+        <v>6982565</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980657</v>
+        <v>117980703</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>97753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593361</v>
+        <v>593374</v>
       </c>
       <c r="R3" t="n">
-        <v>6982517</v>
+        <v>6982518</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980703</v>
+        <v>117980611</v>
       </c>
       <c r="B4" t="n">
-        <v>97753</v>
+        <v>57287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593374</v>
+        <v>593353</v>
       </c>
       <c r="R4" t="n">
-        <v>6982518</v>
+        <v>6982492</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117980691</v>
+        <v>117980702</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593266</v>
+        <v>593324</v>
       </c>
       <c r="R5" t="n">
-        <v>6982565</v>
+        <v>6982544</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980702</v>
+        <v>117980622</v>
       </c>
       <c r="B6" t="n">
-        <v>97753</v>
+        <v>79590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593324</v>
+        <v>593359</v>
       </c>
       <c r="R6" t="n">
-        <v>6982544</v>
+        <v>6982522</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980622</v>
+        <v>117980657</v>
       </c>
       <c r="B7" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593359</v>
+        <v>593361</v>
       </c>
       <c r="R7" t="n">
-        <v>6982522</v>
+        <v>6982517</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 18629-2024 artfynd.xlsx
+++ b/artfynd/A 18629-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980691</v>
+        <v>117980622</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593266</v>
+        <v>593359</v>
       </c>
       <c r="R2" t="n">
-        <v>6982565</v>
+        <v>6982522</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980703</v>
+        <v>117980611</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593374</v>
+        <v>593353</v>
       </c>
       <c r="R3" t="n">
-        <v>6982518</v>
+        <v>6982492</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980611</v>
+        <v>117980657</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593353</v>
+        <v>593361</v>
       </c>
       <c r="R4" t="n">
-        <v>6982492</v>
+        <v>6982517</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117980702</v>
+        <v>117980691</v>
       </c>
       <c r="B5" t="n">
-        <v>97753</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593324</v>
+        <v>593266</v>
       </c>
       <c r="R5" t="n">
-        <v>6982544</v>
+        <v>6982565</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980622</v>
+        <v>117980702</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>97755</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593359</v>
+        <v>593324</v>
       </c>
       <c r="R6" t="n">
-        <v>6982522</v>
+        <v>6982544</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980657</v>
+        <v>117980703</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>97755</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593361</v>
+        <v>593374</v>
       </c>
       <c r="R7" t="n">
-        <v>6982517</v>
+        <v>6982518</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 18629-2024 artfynd.xlsx
+++ b/artfynd/A 18629-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980657</v>
+        <v>117980691</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593361</v>
+        <v>593266</v>
       </c>
       <c r="R2" t="n">
-        <v>6982517</v>
+        <v>6982565</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980703</v>
+        <v>117980657</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593374</v>
+        <v>593361</v>
       </c>
       <c r="R3" t="n">
-        <v>6982518</v>
+        <v>6982517</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980702</v>
+        <v>117980622</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593324</v>
+        <v>593359</v>
       </c>
       <c r="R4" t="n">
-        <v>6982544</v>
+        <v>6982522</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117980691</v>
+        <v>117980611</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593266</v>
+        <v>593353</v>
       </c>
       <c r="R5" t="n">
-        <v>6982565</v>
+        <v>6982492</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,15 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980622</v>
+        <v>117980702</v>
       </c>
       <c r="B6" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593359</v>
+        <v>593324</v>
       </c>
       <c r="R6" t="n">
-        <v>6982522</v>
+        <v>6982544</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,58 +1168,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980611</v>
+        <v>117980703</v>
       </c>
       <c r="B7" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593353</v>
+        <v>593374</v>
       </c>
       <c r="R7" t="n">
-        <v>6982492</v>
+        <v>6982518</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 18629-2024 artfynd.xlsx
+++ b/artfynd/A 18629-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980691</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980657</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980622</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980611</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980702</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,8 +1292,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>